--- a/data/trans_orig/IP07_A11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A11_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8474</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1913</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5631</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8636</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4158</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4778</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12252</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1577</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1682</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4761</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11677</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60740</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66442</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52264</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47108</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55597</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>51875</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49317</t>
+          <t>45899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72823</t>
+          <t>55565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>116938</t>
+          <t>112615</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100225</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125258</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5286</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7850</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4281</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5494</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11194</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5754</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2786</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10787</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40921</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34139</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46246</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42403</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36200</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46843</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34903</t>
+          <t>37249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>84691</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75433</t>
+          <t>75815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>825</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,57 +2134,57 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1659</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3883</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3623</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5415</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5625</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26966</t>
+          <t>30355</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29307</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>24905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>59593</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>53480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6703</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5401</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>23260</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5507</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>22256</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13002</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>20279</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>3282</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8262</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>93857</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>81675</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>102180</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>69,81%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>108997</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>102356</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>113958</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>98215</t>
+          <t>85299</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>79534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106442</t>
+          <t>89402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>179156</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>192146</t>
+          <t>165545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>218309</t>
+          <t>188627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11091</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>3732</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>9062</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3561,107 +3561,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5046</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4949</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>5643</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>12320</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>19280</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>5828</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>2836</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>10144</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,27 +3862,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>69831</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>61373</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>76971</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>80,13%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>70,42%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>50879</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>44776</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>55705</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>81,18%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>71,44%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67187</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>82378</t>
+          <t>56375</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>126088</t>
+          <t>121151</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>116523</t>
+          <t>111212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>134314</t>
+          <t>130114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>3475</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5532</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>5645</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -4356,107 +4356,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>1880</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>1759</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>7441</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>13708</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>29,37%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>9576</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>36358</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>29878</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>40868</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>32938</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>26712</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>36600</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>36876</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>78039</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>25174</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>6394</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>18888</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24606</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>8173</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>10857</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>17694</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>33855</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>10806</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>6079</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>18317</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54490</t>
+          <t>45444</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>44337</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>33963</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>57241</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>14988</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>32062</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>55942</t>
+          <t>33827</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>82603</t>
+          <t>86126</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>332062</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>313244</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>347789</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>75,81%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>84,17%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>314447</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>301810</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>328168</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>82,73%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>347309</t>
+          <t>297213</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>326106</t>
+          <t>282855</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>365372</t>
+          <t>308383</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>661757</t>
+          <t>629275</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>636959</t>
+          <t>608121</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>684623</t>
+          <t>648647</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>469</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
